--- a/MCX_Trading_Platform_Data.xlsx
+++ b/MCX_Trading_Platform_Data.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +437,72 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.179716412037037</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.1797401388888889</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.1797636574074074</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.1797874074074074</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.1798110185185185</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.1798346944212963</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MCX_Trading_Platform_Data.xlsx
+++ b/MCX_Trading_Platform_Data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
         <v>46033</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.179716412037037</v>
+        <v>0.7808441319444445</v>
       </c>
       <c r="C2" t="n">
         <v>-1.5</v>
@@ -453,7 +453,7 @@
         <v>46033</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1797401388888889</v>
+        <v>0.7808679976851851</v>
       </c>
       <c r="C3" t="n">
         <v>-1.5</v>
@@ -464,7 +464,7 @@
         <v>46033</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1797636574074074</v>
+        <v>0.7808914930555555</v>
       </c>
       <c r="C4" t="n">
         <v>-1.5</v>
@@ -475,7 +475,7 @@
         <v>46033</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1797874074074074</v>
+        <v>0.7809153935185185</v>
       </c>
       <c r="C5" t="n">
         <v>-1.5</v>
@@ -486,7 +486,7 @@
         <v>46033</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.1798110185185185</v>
+        <v>0.7809386921296296</v>
       </c>
       <c r="C6" t="n">
         <v>-1.5</v>
@@ -497,9 +497,20 @@
         <v>46033</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1798346944212963</v>
+        <v>0.7809624768518518</v>
       </c>
       <c r="C7" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.780986313125</v>
+      </c>
+      <c r="C8" t="n">
         <v>-1.5</v>
       </c>
     </row>

--- a/MCX_Trading_Platform_Data.xlsx
+++ b/MCX_Trading_Platform_Data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Future Readings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Future Readings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
         <v>46033</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.7808441319444445</v>
+        <v>0.9401232407407407</v>
       </c>
       <c r="C2" t="n">
         <v>-1.5</v>
@@ -453,7 +453,7 @@
         <v>46033</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.7808679976851851</v>
+        <v>0.9401466550925927</v>
       </c>
       <c r="C3" t="n">
         <v>-1.5</v>
@@ -464,7 +464,7 @@
         <v>46033</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.7808914930555555</v>
+        <v>0.940170462962963</v>
       </c>
       <c r="C4" t="n">
         <v>-1.5</v>
@@ -475,7 +475,7 @@
         <v>46033</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.7809153935185185</v>
+        <v>0.9401941782407408</v>
       </c>
       <c r="C5" t="n">
         <v>-1.5</v>
@@ -486,7 +486,7 @@
         <v>46033</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.7809386921296296</v>
+        <v>0.9402182523148148</v>
       </c>
       <c r="C6" t="n">
         <v>-1.5</v>
@@ -497,7 +497,7 @@
         <v>46033</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.7809624768518518</v>
+        <v>0.9402425462962963</v>
       </c>
       <c r="C7" t="n">
         <v>-1.5</v>
@@ -508,9 +508,5982 @@
         <v>46033</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.780986313125</v>
+        <v>0.9402663541666667</v>
       </c>
       <c r="C8" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.9402901273148148</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.9403137499999999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.9403374652777778</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.9403610995370369</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.9403851157407408</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.9404086458333334</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.9404323726851852</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.9404561574074074</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0.9404800925925926</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0.9405039004629629</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0.9405276041666667</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.940551400462963</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.9405751273148149</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.9405993981481482</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.9406228587962964</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.9406470138888889</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.9406704513888888</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.9406943171296297</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.9407179976851853</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.9407418402777777</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.9407654513888888</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.9407889814814815</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0.9408131597222222</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0.9408370717592593</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>0.9408605439814814</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0.9408843171296296</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.9409080671296296</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0.9409316666666666</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.9409582060185185</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>0.9409794907407407</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0.9410029745370371</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>0.9410265972222223</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.9410502430555555</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.9410739699074073</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.9410975231481482</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.9411216203703703</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.9411456018518518</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.9411694444444444</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.9411934375</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>0.9412171643518519</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.9412406250000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0.9412644097222221</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.9412879629629629</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>0.9413113888888889</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0.9413360763888889</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>0.9413592939814814</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>0.941382962962963</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0.9414066550925926</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>0.9414304050925926</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>0.9414540856481481</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0.9414775000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0.9415013888888889</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>0.9415249421296297</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0.9415488425925926</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>0.9415724189814815</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>0.9415960995370372</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.941619675925926</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0.9416435416666666</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0.9416671527777778</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0.9416907523148149</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>0.9417143518518518</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>0.941737974537037</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0.9417615393518518</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>0.9417853125000001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0.9418089699074074</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0.9418329513888889</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>0.9418567245370371</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>0.9418804050925926</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0.9419040162037037</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>0.941927800925926</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0.941951412037037</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0.9419752314814815</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>0.9419987847222223</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>0.9420222916666666</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>0.9420461226851852</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>0.9420698842592593</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>0.9420936689814814</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>0.9421173842592592</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>0.9421408796296296</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>0.9421645949074073</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>0.9421881944444445</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>0.942211851851852</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>0.9422358101851852</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>0.9422596874999999</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>0.9422832986111112</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>0.9423068171296296</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>0.9423308101851852</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>0.9423543055555555</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>0.9423780555555556</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>0.9424022337962963</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>0.942425613425926</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>0.9424494328703703</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>0.9424730208333333</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>0.9424966435185186</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>0.9425204166666666</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>0.9425440625</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>0.9425676967592593</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>0.9425912731481482</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>0.9426151388888889</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>0.9426388078703704</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>0.9426624074074075</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>0.942686574074074</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>0.9427097800925925</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>0.9427335069444445</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>0.9427569907407407</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>0.9427806481481482</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>0.942804837962963</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>0.9428287731481482</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>0.9428523032407408</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>0.9428760416666667</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>0.9428998263888889</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>0.9429233796296297</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>0.9429470138888889</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>0.9429708333333332</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>0.9429943981481481</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>0.9430180671296297</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>0.9430418171296295</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>0.9430653472222222</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>0.9430894907407408</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>0.9431129282407407</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>0.9431366203703704</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>0.9431604166666666</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>0.9431840162037037</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>0.9432078125</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>0.943231550925926</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>0.9432550810185185</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>0.9432786342592593</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>0.943302361111111</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>0.943326238425926</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>0.9433499537037037</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>0.9433736921296295</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>0.9433971180555556</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>0.9434213310185185</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>0.9434448263888889</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>0.9434684953703704</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>0.9434922569444445</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>0.9435160416666666</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>0.9435396990740741</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>0.9435633680555555</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>0.9435868981481481</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>0.9436103356481482</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>0.9436345138888889</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>0.9436578009259259</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>0.9436815277777778</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>0.9437050347222223</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>0.9437284259259259</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>0.9437522222222222</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>0.9437758680555556</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>0.9437996527777777</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>0.9438237615740741</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>0.9438472106481482</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>0.9438708912037038</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>0.9438944328703704</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>0.9439181018518519</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>0.9439418749999999</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>0.9439656712962964</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>0.9439891782407407</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>0.9440132060185185</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>0.9440367708333334</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>0.9440605324074074</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>0.9440842708333332</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>0.9441092708333333</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>0.944133576388889</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>0.9441574189814815</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>0.9441812152777778</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>0.9442046296296296</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>0.9442281944444445</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>0.9442522222222223</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>0.9442764583333334</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>0.9442996875</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>0.9443236458333333</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>0.9443471990740741</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>0.9443710879629629</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>0.9443943634259259</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>0.9444179861111112</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>0.944441886574074</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>0.9444656828703705</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>0.9444896875</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>0.9445129861111112</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>0.9445368634259259</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>0.9445603124999999</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>0.9445839699074073</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>0.9446076157407407</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>0.944631226851852</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>0.9446550810185185</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>0.9446784953703703</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>0.9447022106481481</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>0.9447268055555554</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>0.9447498263888888</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>0.9447735763888889</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>0.944797048611111</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>0.9448208680555555</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>0.9448445717592592</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>0.9448684259259259</v>
+      </c>
+      <c r="C202" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>0.9448919791666667</v>
+      </c>
+      <c r="C203" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>0.9449158101851851</v>
+      </c>
+      <c r="C204" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>0.9449395601851852</v>
+      </c>
+      <c r="C205" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>0.9449631018518519</v>
+      </c>
+      <c r="C206" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>0.9449867476851851</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>0.9450103703703703</v>
+      </c>
+      <c r="C208" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>0.9450338657407408</v>
+      </c>
+      <c r="C209" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>0.9450577083333334</v>
+      </c>
+      <c r="C210" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>0.9450814930555556</v>
+      </c>
+      <c r="C211" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>0.9451052893518518</v>
+      </c>
+      <c r="C212" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>0.9451288310185184</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>0.9451526041666667</v>
+      </c>
+      <c r="C214" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>0.9451761342592592</v>
+      </c>
+      <c r="C215" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>0.9451999652777778</v>
+      </c>
+      <c r="C216" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>0.9452234490740741</v>
+      </c>
+      <c r="C217" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>0.9452468981481481</v>
+      </c>
+      <c r="C218" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>0.9452705555555556</v>
+      </c>
+      <c r="C219" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>0.9452943981481482</v>
+      </c>
+      <c r="C220" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>0.9453179629629629</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>0.9453418981481481</v>
+      </c>
+      <c r="C222" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>0.9453655092592593</v>
+      </c>
+      <c r="C223" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>0.945389386574074</v>
+      </c>
+      <c r="C224" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>0.9454129166666667</v>
+      </c>
+      <c r="C225" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>0.9454365162037036</v>
+      </c>
+      <c r="C226" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>0.9454603703703703</v>
+      </c>
+      <c r="C227" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>0.9454840162037037</v>
+      </c>
+      <c r="C228" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>0.945507337962963</v>
+      </c>
+      <c r="C229" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>0.9455311805555555</v>
+      </c>
+      <c r="C230" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>0.9455548611111111</v>
+      </c>
+      <c r="C231" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>0.9455785763888889</v>
+      </c>
+      <c r="C232" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>0.9456023495370371</v>
+      </c>
+      <c r="C233" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>0.9456261805555556</v>
+      </c>
+      <c r="C234" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>0.9456496759259259</v>
+      </c>
+      <c r="C235" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>0.9456738194444444</v>
+      </c>
+      <c r="C236" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>0.9456973842592593</v>
+      </c>
+      <c r="C237" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>0.9457210763888889</v>
+      </c>
+      <c r="C238" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>0.9457449305555555</v>
+      </c>
+      <c r="C239" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>0.9457684027777777</v>
+      </c>
+      <c r="C240" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>0.9457920717592593</v>
+      </c>
+      <c r="C241" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>0.9458157870370369</v>
+      </c>
+      <c r="C242" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>0.9458403472222222</v>
+      </c>
+      <c r="C243" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>0.9458629398148148</v>
+      </c>
+      <c r="C244" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>0.9458867129629629</v>
+      </c>
+      <c r="C245" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>0.945910324074074</v>
+      </c>
+      <c r="C246" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>0.9459340393518518</v>
+      </c>
+      <c r="C247" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>0.945957662037037</v>
+      </c>
+      <c r="C248" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>0.9459844675925927</v>
+      </c>
+      <c r="C249" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>0.9460049305555556</v>
+      </c>
+      <c r="C250" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>0.9460289120370371</v>
+      </c>
+      <c r="C251" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>0.9460527662037037</v>
+      </c>
+      <c r="C252" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>0.9460762037037037</v>
+      </c>
+      <c r="C253" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>0.9460998032407407</v>
+      </c>
+      <c r="C254" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>0.9461236226851852</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>0.9461473611111111</v>
+      </c>
+      <c r="C256" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>0.946170925925926</v>
+      </c>
+      <c r="C257" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>0.9461946412037038</v>
+      </c>
+      <c r="C258" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>0.9462183680555556</v>
+      </c>
+      <c r="C259" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>0.9462422800925926</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>0.9462658680555556</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>0.9462894907407406</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>0.9463131018518519</v>
+      </c>
+      <c r="C263" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>0.9463369907407407</v>
+      </c>
+      <c r="C264" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>0.9463607523148149</v>
+      </c>
+      <c r="C265" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>0.946384224537037</v>
+      </c>
+      <c r="C266" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>0.9464082407407408</v>
+      </c>
+      <c r="C267" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>0.9464317824074074</v>
+      </c>
+      <c r="C268" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>0.9464555324074074</v>
+      </c>
+      <c r="C269" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>0.9464790393518518</v>
+      </c>
+      <c r="C270" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>0.946503113425926</v>
+      </c>
+      <c r="C271" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>0.9465267129629629</v>
+      </c>
+      <c r="C272" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>0.946550474537037</v>
+      </c>
+      <c r="C273" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>0.9465740046296297</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>0.9465976157407407</v>
+      </c>
+      <c r="C275" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>0.9466212152777779</v>
+      </c>
+      <c r="C276" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>0.9466450231481482</v>
+      </c>
+      <c r="C277" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>0.9466686689814814</v>
+      </c>
+      <c r="C278" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>0.9466921527777779</v>
+      </c>
+      <c r="C279" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>0.9467158333333334</v>
+      </c>
+      <c r="C280" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>0.9467392245370371</v>
+      </c>
+      <c r="C281" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>0.9467630208333333</v>
+      </c>
+      <c r="C282" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>0.9467864583333334</v>
+      </c>
+      <c r="C283" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>0.9468101157407407</v>
+      </c>
+      <c r="C284" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>0.9468339004629629</v>
+      </c>
+      <c r="C285" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>0.9468578356481482</v>
+      </c>
+      <c r="C286" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>0.9468813194444444</v>
+      </c>
+      <c r="C287" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>0.9469046527777778</v>
+      </c>
+      <c r="C288" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>0.9469289583333333</v>
+      </c>
+      <c r="C289" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>0.946952175925926</v>
+      </c>
+      <c r="C290" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>0.9469758564814815</v>
+      </c>
+      <c r="C291" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>0.9469993171296296</v>
+      </c>
+      <c r="C292" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>0.9470230324074074</v>
+      </c>
+      <c r="C293" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>0.9470465972222223</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>0.9470704050925927</v>
+      </c>
+      <c r="C295" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>0.94709375</v>
+      </c>
+      <c r="C296" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>0.9471175347222223</v>
+      </c>
+      <c r="C297" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>0.947141099537037</v>
+      </c>
+      <c r="C298" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>0.9471648495370371</v>
+      </c>
+      <c r="C299" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>0.9471882870370371</v>
+      </c>
+      <c r="C300" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>0.9472120717592594</v>
+      </c>
+      <c r="C301" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>0.9472357986111111</v>
+      </c>
+      <c r="C302" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>0.9472593518518518</v>
+      </c>
+      <c r="C303" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>0.9472832060185186</v>
+      </c>
+      <c r="C304" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>0.9473071180555557</v>
+      </c>
+      <c r="C305" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>0.947330925925926</v>
+      </c>
+      <c r="C306" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>0.9473544097222223</v>
+      </c>
+      <c r="C307" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>0.9473781134259259</v>
+      </c>
+      <c r="C308" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>0.9474018055555556</v>
+      </c>
+      <c r="C309" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>0.9474254629629629</v>
+      </c>
+      <c r="C310" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>0.9474492824074074</v>
+      </c>
+      <c r="C311" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>0.947472650462963</v>
+      </c>
+      <c r="C312" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>0.9474964004629629</v>
+      </c>
+      <c r="C313" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>0.9475199537037037</v>
+      </c>
+      <c r="C314" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>0.947543726851852</v>
+      </c>
+      <c r="C315" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>0.9475675462962962</v>
+      </c>
+      <c r="C316" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>0.9475912037037038</v>
+      </c>
+      <c r="C317" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>0.947615162037037</v>
+      </c>
+      <c r="C318" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>0.9476395023148149</v>
+      </c>
+      <c r="C319" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>0.9476638425925926</v>
+      </c>
+      <c r="C320" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>0.9476869328703703</v>
+      </c>
+      <c r="C321" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>0.9477104861111111</v>
+      </c>
+      <c r="C322" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>0.9477341319444446</v>
+      </c>
+      <c r="C323" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>0.9477580555555556</v>
+      </c>
+      <c r="C324" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B325" s="2" t="n">
+        <v>0.9477815972222222</v>
+      </c>
+      <c r="C325" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>0.9478050115740742</v>
+      </c>
+      <c r="C326" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>0.9478289930555556</v>
+      </c>
+      <c r="C327" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>0.9478524652777777</v>
+      </c>
+      <c r="C328" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>0.9478761342592593</v>
+      </c>
+      <c r="C329" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>0.9478996990740741</v>
+      </c>
+      <c r="C330" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>0.9479236689814814</v>
+      </c>
+      <c r="C331" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>0.9479472685185185</v>
+      </c>
+      <c r="C332" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>0.9479718634259259</v>
+      </c>
+      <c r="C333" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>0.9479949652777778</v>
+      </c>
+      <c r="C334" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>0.9480188078703703</v>
+      </c>
+      <c r="C335" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B336" s="2" t="n">
+        <v>0.9480420833333333</v>
+      </c>
+      <c r="C336" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B337" s="2" t="n">
+        <v>0.9480656481481482</v>
+      </c>
+      <c r="C337" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B338" s="2" t="n">
+        <v>0.9480891666666666</v>
+      </c>
+      <c r="C338" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B339" s="2" t="n">
+        <v>0.9481131365740741</v>
+      </c>
+      <c r="C339" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B340" s="2" t="n">
+        <v>0.9481368518518519</v>
+      </c>
+      <c r="C340" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B341" s="2" t="n">
+        <v>0.9481605787037036</v>
+      </c>
+      <c r="C341" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>0.9481840972222222</v>
+      </c>
+      <c r="C342" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B343" s="2" t="n">
+        <v>0.9482077314814815</v>
+      </c>
+      <c r="C343" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B344" s="2" t="n">
+        <v>0.9482317708333334</v>
+      </c>
+      <c r="C344" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>0.9482551504629629</v>
+      </c>
+      <c r="C345" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>0.9482790625</v>
+      </c>
+      <c r="C346" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>0.9483026388888889</v>
+      </c>
+      <c r="C347" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>0.948326412037037</v>
+      </c>
+      <c r="C348" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>0.9483500578703704</v>
+      </c>
+      <c r="C349" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>0.9483738657407407</v>
+      </c>
+      <c r="C350" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>0.9483976967592592</v>
+      </c>
+      <c r="C351" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>0.9484209375</v>
+      </c>
+      <c r="C352" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>0.9484445833333333</v>
+      </c>
+      <c r="C353" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>0.9484682291666666</v>
+      </c>
+      <c r="C354" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>0.9484918518518518</v>
+      </c>
+      <c r="C355" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>0.948515462962963</v>
+      </c>
+      <c r="C356" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>0.9485391898148148</v>
+      </c>
+      <c r="C357" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>0.9485627314814815</v>
+      </c>
+      <c r="C358" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>0.9485867361111111</v>
+      </c>
+      <c r="C359" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>0.9486107175925926</v>
+      </c>
+      <c r="C360" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>0.9486344097222223</v>
+      </c>
+      <c r="C361" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>0.9486579861111112</v>
+      </c>
+      <c r="C362" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>0.9486813425925926</v>
+      </c>
+      <c r="C363" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>0.9487051157407408</v>
+      </c>
+      <c r="C364" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>0.9487291319444444</v>
+      </c>
+      <c r="C365" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B366" s="2" t="n">
+        <v>0.9487526388888889</v>
+      </c>
+      <c r="C366" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B367" s="2" t="n">
+        <v>0.9487762152777778</v>
+      </c>
+      <c r="C367" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B368" s="2" t="n">
+        <v>0.9488000462962962</v>
+      </c>
+      <c r="C368" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>0.9488234837962963</v>
+      </c>
+      <c r="C369" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B370" s="2" t="n">
+        <v>0.9488472916666667</v>
+      </c>
+      <c r="C370" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B371" s="2" t="n">
+        <v>0.9488710532407407</v>
+      </c>
+      <c r="C371" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B372" s="2" t="n">
+        <v>0.9488948726851852</v>
+      </c>
+      <c r="C372" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B373" s="2" t="n">
+        <v>0.9489190740740739</v>
+      </c>
+      <c r="C373" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B374" s="2" t="n">
+        <v>0.9489425231481482</v>
+      </c>
+      <c r="C374" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B375" s="2" t="n">
+        <v>0.9489661574074075</v>
+      </c>
+      <c r="C375" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B376" s="2" t="n">
+        <v>0.9489897685185186</v>
+      </c>
+      <c r="C376" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B377" s="2" t="n">
+        <v>0.9490132986111111</v>
+      </c>
+      <c r="C377" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>0.949037673611111</v>
+      </c>
+      <c r="C378" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B379" s="2" t="n">
+        <v>0.9490606018518518</v>
+      </c>
+      <c r="C379" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B380" s="2" t="n">
+        <v>0.9490843287037037</v>
+      </c>
+      <c r="C380" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B381" s="2" t="n">
+        <v>0.9491082291666667</v>
+      </c>
+      <c r="C381" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B382" s="2" t="n">
+        <v>0.9491320254629629</v>
+      </c>
+      <c r="C382" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B383" s="2" t="n">
+        <v>0.9491558449074075</v>
+      </c>
+      <c r="C383" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B384" s="2" t="n">
+        <v>0.9491793865740741</v>
+      </c>
+      <c r="C384" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B385" s="2" t="n">
+        <v>0.9492032060185186</v>
+      </c>
+      <c r="C385" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B386" s="2" t="n">
+        <v>0.9492270486111112</v>
+      </c>
+      <c r="C386" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B387" s="2" t="n">
+        <v>0.9492506597222222</v>
+      </c>
+      <c r="C387" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B388" s="2" t="n">
+        <v>0.9492741782407408</v>
+      </c>
+      <c r="C388" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B389" s="2" t="n">
+        <v>0.949297800925926</v>
+      </c>
+      <c r="C389" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B390" s="2" t="n">
+        <v>0.9493215625</v>
+      </c>
+      <c r="C390" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B391" s="2" t="n">
+        <v>0.949345787037037</v>
+      </c>
+      <c r="C391" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B392" s="2" t="n">
+        <v>0.9493694212962962</v>
+      </c>
+      <c r="C392" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B393" s="2" t="n">
+        <v>0.9493930092592592</v>
+      </c>
+      <c r="C393" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B394" s="2" t="n">
+        <v>0.9494166319444444</v>
+      </c>
+      <c r="C394" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B395" s="2" t="n">
+        <v>0.9494404745370371</v>
+      </c>
+      <c r="C395" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B396" s="2" t="n">
+        <v>0.9494639699074074</v>
+      </c>
+      <c r="C396" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B397" s="2" t="n">
+        <v>0.9494877662037037</v>
+      </c>
+      <c r="C397" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B398" s="2" t="n">
+        <v>0.9495110763888889</v>
+      </c>
+      <c r="C398" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B399" s="2" t="n">
+        <v>0.9495349189814815</v>
+      </c>
+      <c r="C399" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B400" s="2" t="n">
+        <v>0.9495589930555556</v>
+      </c>
+      <c r="C400" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B401" s="2" t="n">
+        <v>0.949583136574074</v>
+      </c>
+      <c r="C401" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B402" s="2" t="n">
+        <v>0.9496061805555556</v>
+      </c>
+      <c r="C402" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B403" s="2" t="n">
+        <v>0.9496300694444445</v>
+      </c>
+      <c r="C403" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B404" s="2" t="n">
+        <v>0.9496535879629631</v>
+      </c>
+      <c r="C404" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B405" s="2" t="n">
+        <v>0.9496771759259258</v>
+      </c>
+      <c r="C405" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B406" s="2" t="n">
+        <v>0.9497012152777777</v>
+      </c>
+      <c r="C406" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B407" s="2" t="n">
+        <v>0.9497243750000001</v>
+      </c>
+      <c r="C407" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B408" s="2" t="n">
+        <v>0.9497484722222221</v>
+      </c>
+      <c r="C408" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B409" s="2" t="n">
+        <v>0.9497718402777777</v>
+      </c>
+      <c r="C409" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B410" s="2" t="n">
+        <v>0.9497955439814816</v>
+      </c>
+      <c r="C410" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B411" s="2" t="n">
+        <v>0.9498199768518518</v>
+      </c>
+      <c r="C411" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B412" s="2" t="n">
+        <v>0.9498434490740741</v>
+      </c>
+      <c r="C412" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B413" s="2" t="n">
+        <v>0.9498670370370371</v>
+      </c>
+      <c r="C413" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B414" s="2" t="n">
+        <v>0.9498904050925926</v>
+      </c>
+      <c r="C414" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B415" s="2" t="n">
+        <v>0.9499142013888889</v>
+      </c>
+      <c r="C415" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B416" s="2" t="n">
+        <v>0.9499381018518519</v>
+      </c>
+      <c r="C416" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B417" s="2" t="n">
+        <v>0.949961412037037</v>
+      </c>
+      <c r="C417" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B418" s="2" t="n">
+        <v>0.9499850347222222</v>
+      </c>
+      <c r="C418" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B419" s="2" t="n">
+        <v>0.9500088078703703</v>
+      </c>
+      <c r="C419" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B420" s="2" t="n">
+        <v>0.950032349537037</v>
+      </c>
+      <c r="C420" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B421" s="2" t="n">
+        <v>0.9500561342592593</v>
+      </c>
+      <c r="C421" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B422" s="2" t="n">
+        <v>0.9500803240740741</v>
+      </c>
+      <c r="C422" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B423" s="2" t="n">
+        <v>0.9501035648148148</v>
+      </c>
+      <c r="C423" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B424" s="2" t="n">
+        <v>0.9501270833333333</v>
+      </c>
+      <c r="C424" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>0.9501506597222223</v>
+      </c>
+      <c r="C425" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B426" s="2" t="n">
+        <v>0.9501748726851852</v>
+      </c>
+      <c r="C426" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B427" s="2" t="n">
+        <v>0.9501980324074074</v>
+      </c>
+      <c r="C427" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B428" s="2" t="n">
+        <v>0.9502218055555556</v>
+      </c>
+      <c r="C428" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>0.9502454282407408</v>
+      </c>
+      <c r="C429" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B430" s="2" t="n">
+        <v>0.9502691203703703</v>
+      </c>
+      <c r="C430" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>0.9502931134259259</v>
+      </c>
+      <c r="C431" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>0.9503164120370371</v>
+      </c>
+      <c r="C432" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>0.9503400000000001</v>
+      </c>
+      <c r="C433" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>0.9503639236111111</v>
+      </c>
+      <c r="C434" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>0.9503875115740741</v>
+      </c>
+      <c r="C435" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>0.9504111226851851</v>
+      </c>
+      <c r="C436" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>0.9504352314814816</v>
+      </c>
+      <c r="C437" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B438" s="2" t="n">
+        <v>0.9504586458333333</v>
+      </c>
+      <c r="C438" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B439" s="2" t="n">
+        <v>0.9504826157407408</v>
+      </c>
+      <c r="C439" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B440" s="2" t="n">
+        <v>0.950506099537037</v>
+      </c>
+      <c r="C440" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B441" s="2" t="n">
+        <v>0.9505296412037036</v>
+      </c>
+      <c r="C441" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B442" s="2" t="n">
+        <v>0.9505532060185186</v>
+      </c>
+      <c r="C442" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B443" s="2" t="n">
+        <v>0.9505771527777778</v>
+      </c>
+      <c r="C443" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B444" s="2" t="n">
+        <v>0.9506007060185185</v>
+      </c>
+      <c r="C444" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B445" s="2" t="n">
+        <v>0.950624548611111</v>
+      </c>
+      <c r="C445" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B446" s="2" t="n">
+        <v>0.9506490277777778</v>
+      </c>
+      <c r="C446" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B447" s="2" t="n">
+        <v>0.9506720601851852</v>
+      </c>
+      <c r="C447" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B448" s="2" t="n">
+        <v>0.9506968287037038</v>
+      </c>
+      <c r="C448" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B449" s="2" t="n">
+        <v>0.9507204513888889</v>
+      </c>
+      <c r="C449" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B450" s="2" t="n">
+        <v>0.9507446064814815</v>
+      </c>
+      <c r="C450" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B451" s="2" t="n">
+        <v>0.9507680787037036</v>
+      </c>
+      <c r="C451" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B452" s="2" t="n">
+        <v>0.9507919907407407</v>
+      </c>
+      <c r="C452" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B453" s="2" t="n">
+        <v>0.9508157175925926</v>
+      </c>
+      <c r="C453" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B454" s="2" t="n">
+        <v>0.9508390162037036</v>
+      </c>
+      <c r="C454" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B455" s="2" t="n">
+        <v>0.950863287037037</v>
+      </c>
+      <c r="C455" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B456" s="2" t="n">
+        <v>0.9508866087962963</v>
+      </c>
+      <c r="C456" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B457" s="2" t="n">
+        <v>0.9509102662037037</v>
+      </c>
+      <c r="C457" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B458" s="2" t="n">
+        <v>0.9509337500000001</v>
+      </c>
+      <c r="C458" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B459" s="2" t="n">
+        <v>0.9509572337962963</v>
+      </c>
+      <c r="C459" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B460" s="2" t="n">
+        <v>0.9509809375</v>
+      </c>
+      <c r="C460" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B461" s="2" t="n">
+        <v>0.9510046643518518</v>
+      </c>
+      <c r="C461" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B462" s="2" t="n">
+        <v>0.9510284027777779</v>
+      </c>
+      <c r="C462" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B463" s="2" t="n">
+        <v>0.9510517592592593</v>
+      </c>
+      <c r="C463" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B464" s="2" t="n">
+        <v>0.9510757638888888</v>
+      </c>
+      <c r="C464" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B465" s="2" t="n">
+        <v>0.9510989699074074</v>
+      </c>
+      <c r="C465" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B466" s="2" t="n">
+        <v>0.9511228240740741</v>
+      </c>
+      <c r="C466" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B467" s="2" t="n">
+        <v>0.9511465046296297</v>
+      </c>
+      <c r="C467" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B468" s="2" t="n">
+        <v>0.9511702546296297</v>
+      </c>
+      <c r="C468" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B469" s="2" t="n">
+        <v>0.9511937615740741</v>
+      </c>
+      <c r="C469" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B470" s="2" t="n">
+        <v>0.9512173148148149</v>
+      </c>
+      <c r="C470" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B471" s="2" t="n">
+        <v>0.9512412847222222</v>
+      </c>
+      <c r="C471" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B472" s="2" t="n">
+        <v>0.9512650810185185</v>
+      </c>
+      <c r="C472" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B473" s="2" t="n">
+        <v>0.9512889814814816</v>
+      </c>
+      <c r="C473" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B474" s="2" t="n">
+        <v>0.9513124537037037</v>
+      </c>
+      <c r="C474" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B475" s="2" t="n">
+        <v>0.9513361574074074</v>
+      </c>
+      <c r="C475" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B476" s="2" t="n">
+        <v>0.9513598032407407</v>
+      </c>
+      <c r="C476" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B477" s="2" t="n">
+        <v>0.9513836574074074</v>
+      </c>
+      <c r="C477" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B478" s="2" t="n">
+        <v>0.9514070949074075</v>
+      </c>
+      <c r="C478" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B479" s="2" t="n">
+        <v>0.9514307060185185</v>
+      </c>
+      <c r="C479" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B480" s="2" t="n">
+        <v>0.9514544791666667</v>
+      </c>
+      <c r="C480" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B481" s="2" t="n">
+        <v>0.9514782291666667</v>
+      </c>
+      <c r="C481" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B482" s="2" t="n">
+        <v>0.9515031018518518</v>
+      </c>
+      <c r="C482" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B483" s="2" t="n">
+        <v>0.9515259722222222</v>
+      </c>
+      <c r="C483" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B484" s="2" t="n">
+        <v>0.9515488078703703</v>
+      </c>
+      <c r="C484" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B485" s="2" t="n">
+        <v>0.9515729282407407</v>
+      </c>
+      <c r="C485" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B486" s="2" t="n">
+        <v>0.9515966782407407</v>
+      </c>
+      <c r="C486" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B487" s="2" t="n">
+        <v>0.9516207175925926</v>
+      </c>
+      <c r="C487" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B488" s="2" t="n">
+        <v>0.9516441666666666</v>
+      </c>
+      <c r="C488" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B489" s="2" t="n">
+        <v>0.9516678935185185</v>
+      </c>
+      <c r="C489" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B490" s="2" t="n">
+        <v>0.9516913194444445</v>
+      </c>
+      <c r="C490" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B491" s="2" t="n">
+        <v>0.9517151620370371</v>
+      </c>
+      <c r="C491" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B492" s="2" t="n">
+        <v>0.9517391435185185</v>
+      </c>
+      <c r="C492" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B493" s="2" t="n">
+        <v>0.9517627546296296</v>
+      </c>
+      <c r="C493" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B494" s="2" t="n">
+        <v>0.9517862152777777</v>
+      </c>
+      <c r="C494" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B495" s="2" t="n">
+        <v>0.9518099074074075</v>
+      </c>
+      <c r="C495" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B496" s="2" t="n">
+        <v>0.9518336342592594</v>
+      </c>
+      <c r="C496" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B497" s="2" t="n">
+        <v>0.9518572222222224</v>
+      </c>
+      <c r="C497" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B498" s="2" t="n">
+        <v>0.9518807060185186</v>
+      </c>
+      <c r="C498" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B499" s="2" t="n">
+        <v>0.951904513888889</v>
+      </c>
+      <c r="C499" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B500" s="2" t="n">
+        <v>0.9519278240740741</v>
+      </c>
+      <c r="C500" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B501" s="2" t="n">
+        <v>0.951951550925926</v>
+      </c>
+      <c r="C501" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B502" s="2" t="n">
+        <v>0.9519750925925926</v>
+      </c>
+      <c r="C502" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B503" s="2" t="n">
+        <v>0.9519993402777778</v>
+      </c>
+      <c r="C503" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B504" s="2" t="n">
+        <v>0.9520228124999999</v>
+      </c>
+      <c r="C504" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B505" s="2" t="n">
+        <v>0.9520464004629628</v>
+      </c>
+      <c r="C505" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B506" s="2" t="n">
+        <v>0.9520703009259259</v>
+      </c>
+      <c r="C506" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B507" s="2" t="n">
+        <v>0.952094212962963</v>
+      </c>
+      <c r="C507" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B508" s="2" t="n">
+        <v>0.9521176736111112</v>
+      </c>
+      <c r="C508" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B509" s="2" t="n">
+        <v>0.9521423611111112</v>
+      </c>
+      <c r="C509" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B510" s="2" t="n">
+        <v>0.9521655324074074</v>
+      </c>
+      <c r="C510" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B511" s="2" t="n">
+        <v>0.9521891550925925</v>
+      </c>
+      <c r="C511" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B512" s="2" t="n">
+        <v>0.9522125925925926</v>
+      </c>
+      <c r="C512" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B513" s="2" t="n">
+        <v>0.9522360300925926</v>
+      </c>
+      <c r="C513" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B514" s="2" t="n">
+        <v>0.9522601620370371</v>
+      </c>
+      <c r="C514" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B515" s="2" t="n">
+        <v>0.9522837037037037</v>
+      </c>
+      <c r="C515" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B516" s="2" t="n">
+        <v>0.952307025462963</v>
+      </c>
+      <c r="C516" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B517" s="2" t="n">
+        <v>0.9523305902777778</v>
+      </c>
+      <c r="C517" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B518" s="2" t="n">
+        <v>0.9523551620370371</v>
+      </c>
+      <c r="C518" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B519" s="2" t="n">
+        <v>0.9523781597222222</v>
+      </c>
+      <c r="C519" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B520" s="2" t="n">
+        <v>0.9524018865740741</v>
+      </c>
+      <c r="C520" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>0.9524258333333334</v>
+      </c>
+      <c r="C521" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B522" s="2" t="n">
+        <v>0.9524500694444444</v>
+      </c>
+      <c r="C522" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B523" s="2" t="n">
+        <v>0.9524735416666668</v>
+      </c>
+      <c r="C523" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B524" s="2" t="n">
+        <v>0.9524965162037037</v>
+      </c>
+      <c r="C524" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B525" s="2" t="n">
+        <v>0.9525198842592592</v>
+      </c>
+      <c r="C525" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B526" s="2" t="n">
+        <v>0.9525441319444444</v>
+      </c>
+      <c r="C526" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B527" s="2" t="n">
+        <v>0.9525675694444444</v>
+      </c>
+      <c r="C527" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B528" s="2" t="n">
+        <v>0.9525908680555555</v>
+      </c>
+      <c r="C528" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B529" s="2" t="n">
+        <v>0.9526151157407406</v>
+      </c>
+      <c r="C529" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B530" s="2" t="n">
+        <v>0.9526386689814815</v>
+      </c>
+      <c r="C530" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B531" s="2" t="n">
+        <v>0.9526627893518519</v>
+      </c>
+      <c r="C531" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B532" s="2" t="n">
+        <v>0.9526861805555555</v>
+      </c>
+      <c r="C532" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B533" s="2" t="n">
+        <v>0.9527095717592593</v>
+      </c>
+      <c r="C533" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B534" s="2" t="n">
+        <v>0.9527336458333334</v>
+      </c>
+      <c r="C534" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>0.9527569097222223</v>
+      </c>
+      <c r="C535" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B536" s="2" t="n">
+        <v>0.9527806018518519</v>
+      </c>
+      <c r="C536" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B537" s="2" t="n">
+        <v>0.9528038773148149</v>
+      </c>
+      <c r="C537" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B538" s="2" t="n">
+        <v>0.9528275115740742</v>
+      </c>
+      <c r="C538" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B539" s="2" t="n">
+        <v>0.9528511226851851</v>
+      </c>
+      <c r="C539" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B540" s="2" t="n">
+        <v>0.9528748148148148</v>
+      </c>
+      <c r="C540" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B541" s="2" t="n">
+        <v>0.9528983217592591</v>
+      </c>
+      <c r="C541" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B542" s="2" t="n">
+        <v>0.9529222106481482</v>
+      </c>
+      <c r="C542" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B543" s="2" t="n">
+        <v>0.9529462847222222</v>
+      </c>
+      <c r="C543" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B544" s="2" t="n">
+        <v>0.9529698148148149</v>
+      </c>
+      <c r="C544" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B545" s="2" t="n">
+        <v>0.9529934375</v>
+      </c>
+      <c r="C545" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B546" s="2" t="n">
+        <v>0.9530170949074074</v>
+      </c>
+      <c r="C546" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B547" s="2" t="n">
+        <v>0.9530407060185185</v>
+      </c>
+      <c r="C547" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B548" s="2" t="n">
+        <v>0.9530643402777779</v>
+      </c>
+      <c r="C548" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B549" s="2" t="n">
+        <v>0.9530882407407406</v>
+      </c>
+      <c r="C549" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B550" s="2" t="n">
+        <v>0.9531116550925925</v>
+      </c>
+      <c r="C550" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B551" s="2" t="n">
+        <v>0.9531356209953704</v>
+      </c>
+      <c r="C551" t="n">
         <v>-1.5</v>
       </c>
     </row>
